--- a/Cosmetici/Fiscal/2026-09/Acumuladores_Dominio_Cosmetici_2026.xlsx
+++ b/Cosmetici/Fiscal/2026-09/Acumuladores_Dominio_Cosmetici_2026.xlsx
@@ -10,6 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entradas por CFOP" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Saídas por CFOP" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Serviços por prestador" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contas - entradas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contas - saídas e impostos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contas - serviços" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Entradas por CFOP'!$A$4:$G$35</definedName>
@@ -53,7 +56,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +78,11 @@
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -88,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -98,6 +106,16 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2787,4 +2805,1458 @@
   <autoFilter ref="A4:D40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Contas - entradas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Fonte: Resumo Contábil (sintético) do Domínio, 01/01 a 30/09/2026 (pasta 09_2026). Verde = valor fecha exatamente; azul = pelo nome da conta (confirmar); amarelo = não identificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Acumulador</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>CFOP</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Conta débito</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Conta crédito</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Evidência</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Confiança</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>100 / 101</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>1101 1102 / 2101 2102 2122</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA ou 600 INSUMOS (ICMS: D 30 ICMS A RECUPERAR; IPI: D 29 IPI A RECUPERAR)</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Pelo nome da conta no Resumo Contábil (sem valor que feche) - confirmar. O Resumo tem as duas contas (56: 441.031,19; 600: 84.819,75) e não mostra qual acumulador vai em cada uma</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>média</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>104 / 105 / 107</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>1556 / 2556 / 1407</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (também aparecem 359 escritório, 360 limpeza/copa, 656 EPI, 58 outros materiais)</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Pelo nome da conta no Resumo Contábil (sem valor que feche) - confirmar. A conta parece ir pelo produto, não só pelo acumulador</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>média</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>1411</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>417 (-) DEVOLUÇÃO DE VENDA DE MERCADORIAS</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>504 CLIENTES DIVERSOS (664 COSMETICON quando o cliente é a Cosmeticon)</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Exato: soma do acumulador 02-08/2026 = valor do par no Resumo Contábil 01-09/2026: 390.052,03 = 380.143,70 + 9.908,33</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>133 / 134</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>2202 / 2411</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>415 (-) DEVOLUÇÃO DE VENDA DE PRODUTOS</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>504 CLIENTES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Exato: soma do acumulador 02-08/2026 = valor do par no Resumo Contábil 01-09/2026: 2.312,70 + 10.306,40 = 12.619,10</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>149 / 144</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>1901 / 2901</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>614 ENTRADA P INDUSTRIALIZAÇÃO POR ENCOMENDA</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>607 RETORNO DE MERCADORIA ENVIADA PARA INDUSTRIALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Exato: soma do acumulador 02-08/2026 = valor do par no Resumo Contábil 01-09/2026: 56.948,82 + 16.325,25 = 73.274,07</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>165 / 164</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>1924 / 2924</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>608 REMESSA POR CONTA E ORDEM</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>609 REMESSA POR CONTA E ORDEM</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Exato: soma do acumulador 02-08/2026 = valor do par no Resumo Contábil 01-09/2026: 139.005,39 + 35.347,69 = 174.353,08</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>147 / 148</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>1911 / 2911</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>616 AMOSTRA GRATIS</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Exato: soma do acumulador 02-08/2026 = valor do par no Resumo Contábil 01-09/2026: 37,01 + 156,55 = 193,56</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>2910</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>515 BONIFICAÇÕES RECEBIDAS</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Exato: soma do acumulador 02-08/2026 = valor do par no Resumo Contábil 01-09/2026: 7.550,82</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>1910</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (provável, igual ao 189)</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>515 BONIFICAÇÕES RECEBIDAS</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Sem valor (a única nota foi de R$ 0,00); mesma natureza do 189</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>média</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>1949 / 2949</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>612 REMESSA POR EMPRESTIMOS / OUTROS</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>613 REMESSA POR EMPRESTIMOS / OUTROS</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Exato: soma do acumulador 02-08/2026 = valor do par no Resumo Contábil 01-09/2026: 18.410,35</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>2902</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>607 RETORNO DE MERCADORIA ENVIADA PARA INDUSTRIALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>614 ENTRADA P INDUSTRIALIZAÇÃO POR ENCOMENDA</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Exato: soma do acumulador 02-08/2026 = valor do par no Resumo Contábil 01-09/2026: 41,40</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>2124</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>618 INDUSTRIALIZAÇÃO EFETUADA POR TERCEIROS</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Exato: soma do acumulador 02-08/2026 = valor do par no Resumo Contábil 01-09/2026: 12.212,04 (Color Way, 02/2026)</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>1000 / 1001</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>1352 1353 1932 / 2352 2353</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>312 FRETES E CARRETOS (ICMS do frete: D 30 ICMS A RECUPERAR)</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS (5 CAIXA GERAL quando à vista)</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Pelo nome da conta no Resumo Contábil (sem valor que feche) - confirmar (312 tem 102.651,91; o Acompanhamento 02-08 soma 47.522,10 - faltam meses/notas no que tenho)</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>média</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>1653</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>não identificado</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Combustível R$ 1.532,52 (03/2026): nenhum par do Resumo fecha</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>2922</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>não identificado</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Simples faturamento R$ 5.123,91 (07/2026): nenhum par do Resumo fecha</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>não identificado</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>CFOP sem histórico em 2026</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Contas - saídas e impostos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Fonte: Resumo Contábil (sintético) do Domínio, 01/01 a 30/09/2026 (pasta 09_2026). Verde = valor fecha exatamente; azul = pelo nome da conta (confirmar); amarelo = não identificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Acumulador / imposto</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>CFOP</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Conta débito</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Conta crédito</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Evidência</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Confiança</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>200 / 201 / 202 / 203</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>5101 5102 / 6101 6102 / 5401 / 6401</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>504 CLIENTES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>408 VENDA DE MERCADORIAS</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Par 504 x 408 no Resumo (1.434.018,14)</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>média</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>204 / 205</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>5101 5102 / 5401 (cliente Cosmeticon)</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>664 COSMETICON COMERCIO DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>408 VENDA DE MERCADORIAS</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Par 664 x 408 no Resumo (198.427,30) - conta própria do cliente</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>254 / 255</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>5124 / 6124</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>504 CLIENTES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>411 SERVIÇOS PRESTADOS</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Par 504 x 411 no Resumo (1.615.352,66) - industrialização para terceiros</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>média</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>277 / 217</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>5902 / 6902</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>607 RETORNO DE MERCADORIA ENVIADA PARA INDUSTRIALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>614 ENTRADA P INDUSTRIALIZAÇÃO POR ENCOMENDA</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Par 607 x 614 no Resumo (222.207,12)</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>média</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>207 / 208</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>5910 / 6910</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>514 BONIFICAÇÕES ENVIADAS</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>55 MERCADORIAS PARA VENDA</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Par 514 x 55 no Resumo (38.503,63)</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>média</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>5949</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>612 REMESSA POR EMPRESTIMOS / OUTROS</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>613 REMESSA POR EMPRESTIMOS / OUTROS</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Par 612 x 613 no Resumo (2.354,58)</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>média</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>ICMS das saídas</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr"/>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>426 (-) ICMS</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>172 ICMS A RECOLHER</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Par do Resumo Contábil</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>ICMS-ST das saídas</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>482 (-) SUBSTITUIÇÃO TRIBUTÁRIA</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>481 SUBSTITUIÇÃO TRIBUTÁRIA A RECOLHER</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Par do Resumo Contábil</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>IPI das saídas</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>425 (-) IPI</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>171 IPI A RECOLHER</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Par do Resumo Contábil</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>429 (-) PIS</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>179 PIS A RECOLHER</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Par do Resumo Contábil</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>428 (-) COFINS</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>180 COFINS A RECOLHER</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Par do Resumo Contábil</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>CSLL</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr"/>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>477 (-) CONTRIBUIÇÃO SOCIAL</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>177 CONTRIBUIÇÃO SOCIAL A RECOLHER</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Par do Resumo Contábil</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>IRPJ</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr"/>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>478 (-) IMPOSTO DE RENDA</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>176 IMPOSTO DE RENDA A RECOLHER</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>Par do Resumo Contábil</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>ICMS das entradas (crédito)</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr"/>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>30 ICMS A RECUPERAR</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>conta da mercadoria / frete (56, 312, 618, 612...)</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Par do Resumo Contábil</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>IPI das entradas (crédito)</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr"/>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>29 IPI A RECUPERAR</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>Par do Resumo Contábil</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Apuração ICMS / IPI</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr"/>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>172 ICMS A RECOLHER / 171 IPI A RECOLHER</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>30 ICMS A RECUPERAR / 29 IPI A RECUPERAR</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Par do Resumo Contábil</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>DIFAL (uso e consumo de fora)</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr"/>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>527 ICMS DIFERENCIAL DE ALIQUOTA</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>526 ICMS DIF. DE ALIQUOTA A RECOLHER (crédito: D 30 / C 527)</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Par do Resumo Contábil</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>ISS retido nas NFS-e tomadas</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr"/>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>183 ISS RETIDO A RECOLHER</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Par do Resumo Contábil</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>IRRF retido nas NFS-e tomadas</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>178 IRRF A RECOLHER</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Par do Resumo Contábil</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Contas - serviços</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Serviços tomados: o Resumo sintético não liga a conta ao prestador. Contas de despesa que aparecem contra 506 FORNECEDORES - o vínculo com o acumulador é provável, não confirmado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Conta débito</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Conta crédito</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Valor 01-09/2026 e acumulador provável</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>361 ASSISTÊNCIA CONTÁBIL</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>510 HONORÁRIOS CONTÁBEIS A PAGAR</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>17.000,00 - provável 828 (Protection Assessoria)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>82.167,16 + 10.498,65 (com retenção)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>364 DESPESAS ADMINISTRATIVAS</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>149.107,61 - provável 816 (Flash, créditos de benefícios)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>640 SOFTWARE/SISTEMA</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>24.723,54 - provável 811 CRM, 818 Nextar, 823 Tecnoponto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>576 PLANO DE SAÚDE EMPREGADOS</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>5.188,40 - provável 824 Dental Uni, 821 Plus Santé</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>652 ASSISTENCIA MÉDICA E SOCIAL</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>1.344,50 - provável 831 CMS / 832 Interclin (medicina do trabalho)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>627 DESPESAS LABORATORIAIS</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>1.178,00 - provável 810 Bioactive / Kosmoscience</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>643 PROPAGANDA</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>1.567,76 - provável 830 gráficas</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>325 SERVIÇOS PRESTADOS POR TERCEIROS (custo)</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>2.405,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>321 MANUTENÇÃO E REPARO</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>608,39</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>715 HONORARIOS ADVOCATICIOS</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>1.500,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>618 INDUSTRIALIZAÇÃO EFETUADA POR TERCEIROS</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>12.212,04 (acumulador 199)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Cosmetici/Fiscal/2026-09/Acumuladores_Dominio_Cosmetici_2026.xlsx
+++ b/Cosmetici/Fiscal/2026-09/Acumuladores_Dominio_Cosmetici_2026.xlsx
@@ -13,11 +13,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contas - entradas" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contas - saídas e impostos" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contas - serviços" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contas por fornecedor" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Históricos padrão" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Entradas por CFOP'!$A$4:$G$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Saídas por CFOP'!$A$4:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Serviços por prestador'!$A$4:$D$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contas - entradas'!$A$4:$H$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Contas - serviços'!$A$4:$G$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Contas por fornecedor'!$A$4:$E$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Históricos padrão'!$A$4:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -96,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -114,6 +120,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2813,15 +2825,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2834,551 +2848,1258 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fonte: Resumo Contábil (sintético) do Domínio, 01/01 a 30/09/2026 (pasta 09_2026). Verde = valor fecha exatamente; azul = pelo nome da conta (confirmar); amarelo = não identificado.</t>
+          <t>CONFIRMADO no Domínio: relatório "Lançamentos gerados pela Escrita" 01-09/2026 (Lançamentos.xls, pasta 09_2026) cruzado nota a nota (número + valor) com o Acompanhamento de Entradas. Verde = confirmado; amarelo = sem lançamento/pendente. "Outras contas" = mesmo acumulador, conta diferente por fornecedor/produto (ver aba Contas por fornecedor).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Acumulador</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>CFOP</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Conta débito</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Conta crédito</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Evidência</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Confiança</t>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Acum.</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Débito</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Crédito</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Lançamentos</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Outras contas usadas</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>Situação</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>100 / 101</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>1101 1102 / 2101 2102 2122</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>56 MATÉRIA-PRIMA ou 600 INSUMOS (ICMS: D 30 ICMS A RECUPERAR; IPI: D 29 IPI A RECUPERAR)</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>COMPRA P/ INDUST - DENTRO ESTADO 1.101</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>506 FORNECEDORES DIVERSOS</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Pelo nome da conta no Resumo Contábil (sem valor que feche) - confirmar. O Resumo tem as duas contas (56: 441.031,19; 600: 84.819,75) e não mostra qual acumulador vai em cada uma</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>média</t>
+      <c r="F5" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>600 / 506 (19x)</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>104 / 105 / 107</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>1556 / 2556 / 1407</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>513 MATERIAL DE USO E CONSUMO (também aparecem 359 escritório, 360 limpeza/copa, 656 EPI, 58 outros materiais)</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>COMPRA P/ INDUST - DENTRO ESTADO 1.101</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>506 FORNECEDORES DIVERSOS</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Pelo nome da conta no Resumo Contábil (sem valor que feche) - confirmar. A conta parece ir pelo produto, não só pelo acumulador</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>média</t>
+      <c r="F6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>417 (-) DEVOLUÇÃO DE VENDA DE MERCADORIAS</t>
+          <t>FRETE ESTADUAL</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>504 CLIENTES DIVERSOS (664 COSMETICON quando o cliente é a Cosmeticon)</t>
+          <t>312 FRETES E CARRETOS</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Exato: soma do acumulador 02-08/2026 = valor do par no Resumo Contábil 01-09/2026: 390.052,03 = 380.143,70 + 9.908,33</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>alta</t>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>133 / 134</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>2202 / 2411</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>415 (-) DEVOLUÇÃO DE VENDA DE PRODUTOS</t>
+          <t>FRETE ESTADUAL</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>504 CLIENTES DIVERSOS</t>
+          <t>312 FRETES E CARRETOS</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Exato: soma do acumulador 02-08/2026 = valor do par no Resumo Contábil 01-09/2026: 2.312,70 + 10.306,40 = 12.619,10</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>alta</t>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>149 / 144</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>1901 / 2901</t>
+          <t>107</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>614 ENTRADA P INDUSTRIALIZAÇÃO POR ENCOMENDA</t>
+          <t>COMPRA USO E CONSUMO ST A PRAZO</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>607 RETORNO DE MERCADORIA ENVIADA PARA INDUSTRIALIZAÇÃO</t>
+          <t>513 MATERIAL DE USO E CONSUMO</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Exato: soma do acumulador 02-08/2026 = valor do par no Resumo Contábil 01-09/2026: 56.948,82 + 16.325,25 = 73.274,07</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>alta</t>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>321 / 506 (2x); 360 / 506 (3x)</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>165 / 164</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>1924 / 2924</t>
+          <t>113</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>608 REMESSA POR CONTA E ORDEM</t>
+          <t>DEVOLUÇÃO DE VENDA ST</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>609 REMESSA POR CONTA E ORDEM</t>
+          <t>417 (-) DEVOLUÇÃO DE VENDA DE MERCADORIAS</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Exato: soma do acumulador 02-08/2026 = valor do par no Resumo Contábil 01-09/2026: 139.005,39 + 35.347,69 = 174.353,08</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>alta</t>
+          <t>664 COSMETICON</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>417 / 504 (2x)</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>147 / 148</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>1911 / 2911</t>
+          <t>104</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>56 MATÉRIA-PRIMA</t>
+          <t>COMPRA USO E CONSUMO DENTRO DO ESTADO</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>616 AMOSTRA GRATIS</t>
+          <t>513 MATERIAL DE USO E CONSUMO</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Exato: soma do acumulador 02-08/2026 = valor do par no Resumo Contábil 01-09/2026: 37,01 + 156,55 = 193,56</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>alta</t>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>359 / 506 (4x); 360 / 506 (7x); 656 / 506 (4x); 321 / 506 (3x); 58 / 506 (1x); 627 / 506 (2x); 596 / 506 (1x)</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>192</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>56 MATÉRIA-PRIMA</t>
+          <t>COMPRA COMBUSTIVEL PARA IND. A PRAZO</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>515 BONIFICAÇÕES RECEBIDAS</t>
+          <t>513 MATERIAL DE USO E CONSUMO</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Exato: soma do acumulador 02-08/2026 = valor do par no Resumo Contábil 01-09/2026: 7.550,82</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>alta</t>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>1901</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>ENTRADA PARA IND. POR ENCOMENDA - 1901</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>614 ENTRADA P INDUSTRIALIZAÇÃO POR ENCOMENDA</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>607 RETORNO DE MERCADORIA ENVIADA PARA INDUSTRIALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>1910</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>1910</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>56 MATÉRIA-PRIMA (provável, igual ao 189)</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>515 BONIFICAÇÕES RECEBIDAS</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>Sem valor (a única nota foi de R$ 0,00); mesma natureza do 189</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>média</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>1949 / 2949</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>612 REMESSA POR EMPRESTIMOS / OUTROS</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>613 REMESSA POR EMPRESTIMOS / OUTROS</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>Exato: soma do acumulador 02-08/2026 = valor do par no Resumo Contábil 01-09/2026: 18.410,35</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>alta</t>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>ENTRADA DE BONIF. DOAÇÃO E BRINDE 1.910</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+      <c r="E14" s="10" t="inlineStr"/>
+      <c r="F14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="10" t="inlineStr"/>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>sem lançamento no período</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>147</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>607 RETORNO DE MERCADORIA ENVIADA PARA INDUSTRIALIZAÇÃO</t>
+          <t>ENTRADA AMOSTRA GRATIS - 1911</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>614 ENTRADA P INDUSTRIALIZAÇÃO POR ENCOMENDA</t>
+          <t>56 MATÉRIA-PRIMA</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Exato: soma do acumulador 02-08/2026 = valor do par no Resumo Contábil 01-09/2026: 41,40</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>alta</t>
+          <t>616 AMOSTRA GRATIS</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>ENTRADA P/ IND POR CONTA E ORDEM - 1924</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>608 REMESSA POR CONTA E ORDEM</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>609 REMESSA POR CONTA E ORDEM</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>1932</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>FRETE ESTADUAL</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>312 FRETES E CARRETOS</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>OUTRAS ENTRADAS DE MERCADORIAS - 949</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>612 REMESSA POR EMPRESTIMOS / OUTROS</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>613 REMESSA POR EMPRESTIMOS / OUTROS</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>COMPRA P/ INDUST - FORA ESTADO 2.101</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>600 / 506 (1x)</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>COMPRA P/ INDUST - FORA ESTADO 2.101</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>600 / 506 (2x)</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>2122</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>COMPRA P/ INDUST - FORA ESTADO 2.101</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>2124</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>2124</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>sem descrição nos relatórios - confirmar n</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>618 INDUSTRIALIZAÇÃO EFETUADA POR TERCEIROS</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>506 FORNECEDORES DIVERSOS</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>Exato: soma do acumulador 02-08/2026 = valor do par no Resumo Contábil 01-09/2026: 12.212,04 (Color Way, 02/2026)</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>1000 / 1001</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>1352 1353 1932 / 2352 2353</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>312 FRETES E CARRETOS (ICMS do frete: D 30 ICMS A RECUPERAR)</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>506 FORNECEDORES DIVERSOS (5 CAIXA GERAL quando à vista)</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Pelo nome da conta no Resumo Contábil (sem valor que feche) - confirmar (312 tem 102.651,91; o Acompanhamento 02-08 soma 47.522,10 - faltam meses/notas no que tenho)</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>média</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>1653</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>não identificado</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="F22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>DEVOLUÇÃO INTERESTADUAL 2.202</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>415 (-) DEVOLUÇÃO DE VENDA DE PRODUTOS</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>504 CLIENTES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>2352</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>FRETE INTERESTADUAL</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>312 FRETES E CARRETOS</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>506 FORNECEDORES DIVERSOS</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>Combustível R$ 1.532,52 (03/2026): nenhum par do Resumo fecha</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F24" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>2353</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>FRETE INTERESTADUAL</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>312 FRETES E CARRETOS</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>2411</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>DEVOLUÇÃO INTERESTADUAL C/ ST</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>415 (-) DEVOLUÇÃO DE VENDA DE PRODUTOS</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>504 CLIENTES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>2556</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>COMPRA USO E CONSUMO FORA DO ESTADO</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>2901</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>ENTRADA PARA IND. POR ENCOMENDA - 2901</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>614 ENTRADA P INDUSTRIALIZAÇÃO POR ENCOMENDA</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>607 RETORNO DE MERCADORIA ENVIADA PARA INDUSTRIALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>2902</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>RETORNO DE MERC. REM. PARA INDUST. 2.902</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>607 RETORNO DE MERCADORIA ENVIADA PARA INDUSTRIALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>614 ENTRADA P INDUSTRIALIZAÇÃO POR ENCOMENDA</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>2910</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>ENTRADA DE BONIF, DOAÇÃO E BRINDE - 2910</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>515 BONIFICAÇÕES RECEBIDAS</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>2911</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>ENTRADA AMOSTRA GRATIS - 2911</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>616 AMOSTRA GRATIS</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>2922</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>ENTRADA SIMPLES FAT. ENTR FUTURA .922</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr"/>
+      <c r="E32" s="10" t="inlineStr"/>
+      <c r="F32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="10" t="inlineStr"/>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>sem lançamento no período</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>ENTRADA P/ IND POR CONTA E ORDEM - 2924</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>608 REMESSA POR CONTA E ORDEM</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>609 REMESSA POR CONTA E ORDEM</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>2949</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>OUTRAS ENTRADAS DE MERCADORIAS - 949</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>612 REMESSA POR EMPRESTIMOS / OUTROS</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>613 REMESSA POR EMPRESTIMOS / OUTROS</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>sem acumulador em 2026</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr"/>
+      <c r="E35" s="10" t="inlineStr"/>
+      <c r="F35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="10" t="inlineStr"/>
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>pendente</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>2922</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>não identificado</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>506 FORNECEDORES DIVERSOS</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>Simples faturamento R$ 5.123,91 (07/2026): nenhum par do Resumo fecha</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>pendente</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>não identificado</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr"/>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>CFOP sem histórico em 2026</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>pendente</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A4:H35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4013,12 +4734,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4031,232 +4756,3979 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Serviços tomados: o Resumo sintético não liga a conta ao prestador. Contas de despesa que aparecem contra 506 FORNECEDORES - o vínculo com o acumulador é provável, não confirmado.</t>
+          <t>CONFIRMADO no Domínio: relatório "Lançamentos gerados pela Escrita" 01-09/2026 (Lançamentos.xls, pasta 09_2026) cruzado nota a nota (número + valor) com o Acompanhamento de Entradas. NFS-e com ISS retido: D despesa (total) / C 506 (líquido) / C 183 (ISS); IRRF: D 506 / C 178.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Conta débito</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Conta crédito</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Valor 01-09/2026 e acumulador provável</t>
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Acum.</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Prestadores</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Débito</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Crédito</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Lançamentos</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Observação</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Situação</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>CALIBRABEM LTDA, VON GRAFFEN E CREVELLONI LTD</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr"/>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>PENSU EXACTU COMERCIO E SERV, CMS CONSULTORIA EM MEDICINA,, PROTECTION ASSESSORIA EMPRES</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F6" s="9" t="inlineStr"/>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>ECOLOGICA DESTINACAO DE RESI, ESGOFOSSA DESENTUPIDORA LTDA</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>multipartida com ISS retido: D despesa / C 506 líquido / C 183 ISS</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>BIO CONTROL CONTROLE BIOLOGI</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9" t="inlineStr"/>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>ASSOCIACAO COMERCIAL E INDUS</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="9" t="inlineStr"/>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KOSMOSCIENCE CIENCIA E TECNO, BIOACTIVE - BIOTECNOLOGIA E </t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="9" t="inlineStr"/>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>811</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>CRM TECNOLOGIA EM SISTEMAS D</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>640 SOFTWARE/SISTEMA</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" s="9" t="inlineStr"/>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>TNT MERCURIO CARGAS E ENCOME, RAPIDO ABC TRANSPORTES LTDA</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>312 FRETES E CARRETOS</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="9" t="inlineStr"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>HOTEL VALE BOA VISTA LTDA, RA PORTO MAR HOTEL LTDA</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>364 DESPESAS ADMINISTRATIVAS</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="9" t="inlineStr"/>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>FLASH TECNOLOGIA E  INSTITUI</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>364 DESPESAS ADMINISTRATIVAS</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="F14" s="9" t="inlineStr"/>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>VR BENEFICIOS E SERVICOS DE , NEXTAR TECNOLOGIA DE SOFTWAR</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>364 DESPESAS ADMINISTRATIVAS</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>LIGGA TELECOMUNICACOES S.A., LIGGA SERVICOS EM TELECOM S.</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="9" t="inlineStr"/>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>LIGGA TELECOMUNICACOES S.A., LIGGA SERVICOS EM TELECOM S.</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>643 PROPAGANDA</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="9" t="inlineStr"/>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>PLUS SANTE EMERGENCIAS MEDIC</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>576 PLANO DE SAÚDE EMPREGADOS</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" s="9" t="inlineStr"/>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>TECNOPONTO TECNOLOGIA AVANCA</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>640 SOFTWARE/SISTEMA</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" s="9" t="inlineStr"/>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>DENTAL UNI - COOPERATIVA ODO</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>652 ASSISTENCIA MÉDICA E SOCIAL</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="9" t="inlineStr"/>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>ANDRADE ENGENHARIA LTDA.</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>364 DESPESAS ADMINISTRATIVAS</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" s="9" t="inlineStr"/>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>INSETCONTROL CONTROLE DE PRA, INSETCONTROL SERVICOS DE HIG</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="9" t="inlineStr"/>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>PROTECTION ASSESSORIA EMPRES</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>361 ASSISTÊNCIA CONTÁBIL</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>510 HONORÁRIOS CONTÁBEIS A PAGAR</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>17.000,00 - provável 828 (Protection Assessoria)</t>
-        </is>
-      </c>
+      <c r="E23" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="9" t="inlineStr"/>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>GRAFICA EXPRESS LTDA, OFICINA DO IMPRESSO GRAFICA , TIPOGRAFIA IGUACU LTDA</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>325 SERVIÇOS PRESTADOS POR TERCEIROS (custo)</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="9" t="inlineStr"/>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>CMS CONSULTORIA EM MEDICINA,</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="9" t="inlineStr"/>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INTERCLIN SERVICOS DE SAUDE </t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>576 PLANO DE SAÚDE EMPREGADOS</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>506 FORNECEDORES DIVERSOS</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="9" t="inlineStr"/>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>GENESIS ALIANCA SERVICOS MEDICOS (67.742.984/0001-57)</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr"/>
+      <c r="D27" s="10" t="inlineStr"/>
+      <c r="E27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>sem histórico</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>GL HOTEIS (48.395.289/0001-11)</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr"/>
+      <c r="D28" s="10" t="inlineStr"/>
+      <c r="E28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>sem histórico - hotéis (815) foram em 364</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>DOM RICARDO HOTEL (01.790.040/0001-47)</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr"/>
+      <c r="D29" s="10" t="inlineStr"/>
+      <c r="E29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>sem histórico - hotéis (815) foram em 364</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>EXTRALAB (04.665.405/0001-08)</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr"/>
+      <c r="D30" s="10" t="inlineStr"/>
+      <c r="E30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>sem histórico; retenção PIS/COFINS/CSLL sem conta no Domínio</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G30"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E125"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Contas por fornecedor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Conta usada pelo Domínio para cada fornecedor (compras, uso e consumo, serviços) - fornecedores.json "contas_dominio". Regra: embalagem/rótulo → 600 INSUMOS; químico → 56 MATÉRIA-PRIMA; uso e consumo → 513, exceto escritório 359, limpeza 360, EPI 656, manutenção 321.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>CNPJ</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Fornecedor</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Conta(s) no Domínio</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Atenção</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>54079636000108</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>AGATHA INDUSTRIA DE MANUFATURADOS LTDA</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (1x)</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>506 FORNECEDORES DIVERSOS</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>82.167,16 + 10.498,65 (com retenção)</t>
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>15524335000186</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>AJ SOLUCOES E EMBALAGENS LTDA</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (3x), 58 OUTROS MATERIAIS DE CONSUMO INDUSTRIAL (1x)</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>misto - conferir o produto</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>364 DESPESAS ADMINISTRATIVAS</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>506 FORNECEDORES DIVERSOS</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>149.107,61 - provável 816 (Flash, créditos de benefícios)</t>
-        </is>
-      </c>
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>15524335000186</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>AJ SOLUCOES E EMBALAGENS LTDA</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>640 SOFTWARE/SISTEMA</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>506 FORNECEDORES DIVERSOS</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>24.723,54 - provável 811 CRM, 818 Nextar, 823 Tecnoponto</t>
-        </is>
-      </c>
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>16987597000140</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>ALLOXY ESPECIALIDADES QUIMICAS LTDA</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (4x)</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>576 PLANO DE SAÚDE EMPREGADOS</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>506 FORNECEDORES DIVERSOS</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>5.188,40 - provável 824 Dental Uni, 821 Plus Santé</t>
-        </is>
-      </c>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>93763555000508</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>ALPHA QUIMICA LTDA</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>652 ASSISTENCIA MÉDICA E SOCIAL</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>506 FORNECEDORES DIVERSOS</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>1.344,50 - provável 831 CMS / 832 Interclin (medicina do trabalho)</t>
-        </is>
-      </c>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>43165042000195</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>AMONEX DO BRASIL IND E COM LTDA</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>627 DESPESAS LABORATORIAIS</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>506 FORNECEDORES DIVERSOS</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>1.178,00 - provável 810 Bioactive / Kosmoscience</t>
-        </is>
-      </c>
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>80402860000190</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>ANDRADE ENGENHARIA LTDA.</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>364 DESPESAS ADMINISTRATIVAS (8x)</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>643 PROPAGANDA</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>506 FORNECEDORES DIVERSOS</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>1.567,76 - provável 830 gráficas</t>
-        </is>
-      </c>
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>01142107000137</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>AQIA QUIMICA INOVATIVA LTDA</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (6x)</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>325 SERVIÇOS PRESTADOS POR TERCEIROS (custo)</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>506 FORNECEDORES DIVERSOS</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>2.405,00</t>
-        </is>
-      </c>
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>08644416000154</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>ARGILAS DO BRASIL COMERCIO DE INSUMOS LTDA</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>321 MANUTENÇÃO E REPARO</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>506 FORNECEDORES DIVERSOS</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>608,39</t>
-        </is>
-      </c>
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>95344503000190</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASSOCIACAO COMERCIAL E INDUSTRIAL DE FAZENDA </t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS (1x)</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>715 HONORARIOS ADVOCATICIOS</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>506 FORNECEDORES DIVERSOS</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>1.500,00</t>
-        </is>
-      </c>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>75176859000236</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>AUTO POSTO E MECANICA BARAO LTDA</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (10x)</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>618 INDUSTRIALIZAÇÃO EFETUADA POR TERCEIROS</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>506 FORNECEDORES DIVERSOS</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>12.212,04 (acumulador 199)</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>75176859000236</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>AUTO POSTO E MECANICA BARAO LTDA</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (7x)</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>69170462000668</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>BARENTZ BRASIL DISTRIBUIDORA LTDA</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (3x)</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>09116873000139</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>BIO CONTROL CONTROLE BIOLOGICO DE AMBIENTES L</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS (2x)</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>59684382000162</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>BIOACTIVE - BIOTECNOLOGIA E DESENVOLVIMENTO D</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS (7x)</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>01399482000167</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>BRAL-MAX INDUSTRIA E COMERCIO DE PLASTICOS LT</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>03421909000101</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>BRENNTAG SPECIALTIES BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (2x)</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>03364555000100</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>C-PACK CREATIVE PACKAGING SA</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (2x)</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>37295717000118</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>CAETANO PLASTICOS EMBALAGENS LTDA</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>600 INSUMOS (1x)</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>19691420000190</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>CALIBRABEM LTDA</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS (1x)</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>58309709000820</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>CHEMYUNION LTDA</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (2x)</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>21440288000195</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>CMS CONSULTORIA EM MEDICINA, SEGURANCA DO TRA</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS (6x)</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>05086085000196</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>COMERCIO DE METAIS METAL TROM LTDA</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>77765840000501</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>CONTABILISTA SUPRIMENTOS CORPORATIVOS S.A.</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>359 MATERIAL DE ESCRITÓRIO (2x)</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>24891333000116</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>CRM TECNOLOGIA EM SISTEMAS DE INFORMACAO LTDA</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>640 SOFTWARE/SISTEMA (9x)</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>74581091000809</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>DAXIA DOCE AROMA INDUSTRIA E COMERCIO LTDA</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>58456476000111</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>DECORBEL INDUSTRIA E COMERCIO DE EMBALAGENS E</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>600 INSUMOS (3x)</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>78738101000151</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>DENTAL UNI - COOPERATIVA ODONTOLOGICA</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>652 ASSISTENCIA MÉDICA E SOCIAL (8x)</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>77172161000510</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>DEPOSITO DE MATERIAIS PARA CONSTRUCAO NICHELE</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (4x), 321 MANUTENÇÃO E REPARO (1x)</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>misto - conferir o produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>04993269000177</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA INDUSTRIAL PARANAENSE LTDA</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (4x)</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>16935723000112</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>DISTRIOL - INDUSTRIA E COMERCIO LTDA</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (2x)</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>02074242000155</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>E.J. KRIEGER E CIA LTDA</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>03730493000294</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECOLOGICA DESTINACAO DE RESIDUOS INDUSTRIAIS </t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS (2x)</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>22255622000101</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>ECOPLUS - LAVANDERIA INDUSTRIAL LTDA</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS (1x)</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>85014793000312</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELETRORASTRO COMERCIO DE MATERIAIS ELETRICOS </t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (5x), 321 MANUTENÇÃO E REPARO (2x)</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>misto - conferir o produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>49547438000183</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>ELLOLIMP COMERCIO DE PRODUTOS DE HIGIENE E LI</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (2x)</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>91389460000109</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>EMBACAPS QUIMICA E FARMACEUTICA LTDA - RS</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (6x)</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>91389460000451</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>EMBACAPS QUIMICA E FARMACEUTICA LTDA - SP</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (3x)</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>10625467000180</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>EMUNA COMERCIO DE PRODUTOS QUIMICOS LTDA</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>54550401000144</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>EQUISUL EQUIPAMENTOS E SUPRIMENTOS INDUSTRIAI</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>656 EPI (3x), 513 MATERIAL DE USO E CONSUMO (1x)</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>misto - conferir o produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>27827087000121</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>ESGOFOSSA DESENTUPIDORA LTDA</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS (3x)</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>03147393002950</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>ESTRE AMBIENTAL S/A EM RECUPERACAO JUDICIAL</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS (2x)</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>76509488000149</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>FARMANILQUIMA COM. ANILINAS E PRODS.QUIM.LTDA</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>00997332000192</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>FAV105 - FRAGRANCES LTDA</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>32475507000198</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>FERNANDO BARGUENO SOCIEDADE INDIVIDUAL DE ADV</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>715 HONORARIOS ADVOCATICIOS (1x)</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>32223020000118</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLASH TECNOLOGIA E  INSTITUICAO DE PAGAMENTO </t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>364 DESPESAS ADMINISTRATIVAS (19x)</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>10693887000447</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>FOCUS TECNOLOGIA COMERCIAL QUIMICA LTDA</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (2x)</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>03050199000150</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>G.A MACHADO &amp; CIA LTDA</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>359 MATERIAL DE ESCRITÓRIO (1x)</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>41592907000174</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>GAMBOA INDUSTRIA DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>81713836000135</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>GRAFICA EXPRESS LTDA</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>325 SERVIÇOS PRESTADOS POR TERCEIROS (custo) (1x)</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>67548693000122</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>HIGH CHEM COM. E IND. DE PRODS. QUIMICOS LTDA</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (3x)</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>05251279000108</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>HOTEL VALE BOA VISTA LTDA</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>364 DESPESAS ADMINISTRATIVAS (1x)</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>18858535000163</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>HS INKLASER LTDA</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (3x)</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>10265455000192</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>ILS TECNOLOGIA EM EQUIP DE SEG DO TRABALHO LT</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>656 EPI (1x), 513 MATERIAL DE USO E CONSUMO (1x)</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>misto - conferir o produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>60874724000943</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>INDUSTRIA QUIMICA  ANASTACIO S/A</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>06216467000150</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>INNOVARTH COMERCIO DE PRODUTOS QUIMICOS LTDA.</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (2x)</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>14309879000162</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>INSETCONTROL CONTROLE DE PRAGAS LTDA ME</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS (8x)</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>46022110000155</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>INTERCLIN SERVICOS DE SAUDE LTDA</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>576 PLANO DE SAÚDE EMPREGADOS (1x)</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>46849303000184</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>INTERLAB DISTR. PROD. CIENTIFICOS LTDA.</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (2x)</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>46849303000184</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>INTERLAB DISTR. PROD. CIENTIFICOS LTDA.</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (1x)</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>93408003000140</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>JOVII COSMECEUTICA LTDA</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>80970842953</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>JUAREZ ANTONIO POLLI</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (1x)</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>05944444000107</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KOSMOSCIENCE CIENCIA E TECNOLOGIA COSMETICA, </t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS (2x)</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>64949480000114</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>L ESSENCE INDUSTRIA E COMERCIO LTDA</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (3x)</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>25117305000109</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>L.H.S.G. COMERCIO DE COMBUSTIVEIS EIRELI</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (1x)</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>08044874000152</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>LABAZ CIENTIFICA LTDA</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (5x)</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>65649511000184</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>LIGGA SERVICOS EM TELECOM S.A.</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>643 PROPAGANDA (3x), 362 SERVIÇOS PRESTADOS POR TERCEIROS (3x)</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>misto - conferir o produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>04368865000166</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>LIGGA TELECOMUNICACOES S.A.</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS (5x), 643 PROPAGANDA (5x)</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>misto - conferir o produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>42251346000102</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>LP MOTOPECAS LTDA</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (1x)</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>35634515000128</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>MAIAN INDUSTRIA DE PRODUTOS QUIMICOS LTDA</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (2x)</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>04196584000173</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>MASTER PUMPS EMB COM. IMP. EXP. LTDA</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>78762994000170</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>MATIZAPLAST PLASTICOS E CORANTES LTDA</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (4x)</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>49698723003110</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>MCASSAB COMERCIO E INDUSTRIA LTDA</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>49698723001177</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>MCASSAB COMERCIO E INDUSTRIA LTDA</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>54446026000197</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>MULTIQUIM INDUSTRIA COMERCIO IMPORTACAO E EXP</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>39290181000173</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>NEOSENSE FRAGRANCIAS LTDA</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>04580911000196</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>NEXTAR TECNOLOGIA DE SOFTWARE LTDA</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>364 DESPESAS ADMINISTRATIVAS (5x)</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>09220921000304</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>NOVA PIRAMIDAL THERMOPLASTICS LTDA</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>09220921000215</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>NOVA PIRAMIDAL THERMOPLASTICS LTDA</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (7x)</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>21012134000100</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>OAK FRAGRANCES IND E COM IMPORTACAO E EXPORTA</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>00495545000116</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>OFICINA DO IMPRESSO GRAFICA E EDITORA LTDA.</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>325 SERVIÇOS PRESTADOS POR TERCEIROS (custo) (1x)</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>07768652000110</t>
+        </is>
+      </c>
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>PENSU EXACTU COMERCIO E SERVICOS DE EQUIPAMEN</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS (8x)</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>33598527000119</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>PIZZA PACK COMERCIO DE EMBALAGENS EIRELI</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>600 INSUMOS (6x)</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>04523560000181</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>PLUS SANTE EMERGENCIAS MEDICAS S.A.</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>576 PLANO DE SAÚDE EMPREGADOS (8x)</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>76549872000175</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>POSTO UMBARA LTDA</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (1x)</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>42628591000196</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>PROTECTION ASSESSORIA EMPRESARIAL LTDA</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>361 ASSISTÊNCIA CONTÁBIL (6x), 362 SERVIÇOS PRESTADOS POR TERCEIROS (3x)</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>misto - conferir o produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>11340087000162</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>PROVITAL DO BRASIL COM. DE INSUMOS PARA COSME</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (6x)</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>05991338000176</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="inlineStr">
+        <is>
+          <t>QUIMIFORMULA COM DE PROD QUIM LTDA..</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (3x)</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>17666331000168</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>R&amp;S COMERCIO DE COSMETICOS</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (1x)</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>63874006000108</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>RA PORTO MAR HOTEL LTDA</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>364 DESPESAS ADMINISTRATIVAS (2x)</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>92025246000560</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>RAPIDO ABC TRANSPORTES LTDA</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>312 FRETES E CARRETOS (2x)</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>62341566000134</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>REATEC DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (7x)</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>62341566000134</t>
+        </is>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>REATEC DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (3x), 627 DESPESAS LABORATORIAIS (2x)</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="inlineStr">
+        <is>
+          <t>misto - conferir o produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t>78004553000100</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>RECOZIL COMERCIO DE EMBALAGENS LTDA</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>600 INSUMOS (1x)</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>55680778000180</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>RIF MOTOS &amp; ACESSORIOS LTDA - MATRIZ</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (2x)</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>78371747000143</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>ROCCOPLAN PAPELARIA LTDA</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>359 MATERIAL DE ESCRITÓRIO (1x)</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>01876559000142</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>SARFAM INDUSTRIA COMERCIO E IMPORTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="12" t="inlineStr">
+        <is>
+          <t>59087034000108</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>SAVATEC COMERCIO E SERVICOS LTDA</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS (1x)</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>59087034000108</t>
+        </is>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>SAVATEC COMERCIO E SERVICOS LTDA</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (5x), 596 CUSTOS DOS PRODUTOS VENDIDOS (1x)</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>misto - conferir o produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>30815069000134</t>
+        </is>
+      </c>
+      <c r="B104" s="10" t="inlineStr">
+        <is>
+          <t>SB DISTRIBUIDORA LTDA</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>360 MATERIAL DE HIGIENE E LIMPEZA / COPA (4x), 513 MATERIAL DE USO E CONSUMO (2x)</t>
+        </is>
+      </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>misto - conferir o produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>62514971000107</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>SCENTEC ESSENCIAS E FRAGRANCIAS LTDA</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="12" t="inlineStr">
+        <is>
+          <t>62705276000122</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>SCLARSKI COMERCIO LTDA</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>600 INSUMOS (1x)</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t>03402014000120</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>SOLABIA BIOTECNOLOGICA</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t>62667991000118</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>SOMMA PRODUTOS PROFISSIONAIS PARA LIMPEZA LTD</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>360 MATERIAL DE HIGIENE E LIMPEZA / COPA (4x)</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>12924620000104</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>STEELPACK GROUP BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>600 INSUMOS (2x)</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>01898598000493</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>STEPAN QUIMICA LTDA</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>25141658000144</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>SUL TAPE COMERCIO DE EMBALAGENS EIRELI</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (3x)</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="12" t="inlineStr">
+        <is>
+          <t>18323476000129</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>SUMMIT COSMETICS LATIN   AMERICA ESPEC. COSME</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (4x)</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>73419905000174</t>
+        </is>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO BOZA LTDA</t>
+        </is>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>360 MATERIAL DE HIGIENE E LIMPEZA / COPA (2x), 513 MATERIAL DE USO E CONSUMO (2x)</t>
+        </is>
+      </c>
+      <c r="E113" s="10" t="inlineStr">
+        <is>
+          <t>misto - conferir o produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="12" t="inlineStr">
+        <is>
+          <t>78413325001246</t>
+        </is>
+      </c>
+      <c r="B114" s="12" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO JACOMAR LTDA</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (1x)</t>
+        </is>
+      </c>
+      <c r="E114" s="12" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>77800407000128</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>TECNOPONTO TECNOLOGIA AVANCADA EM CONTROLE DE</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>640 SOFTWARE/SISTEMA (7x)</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="12" t="inlineStr">
+        <is>
+          <t>77800407000128</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="inlineStr">
+        <is>
+          <t>TECNOPONTO TECNOLOGIA AVANCADA EM CONTROLE DE</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (1x)</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>75114363000157</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>TIPOGRAFIA IGUACU LTDA</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>325 SERVIÇOS PRESTADOS POR TERCEIROS (custo) (1x)</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="12" t="inlineStr">
+        <is>
+          <t>95591723018328</t>
+        </is>
+      </c>
+      <c r="B118" s="12" t="inlineStr">
+        <is>
+          <t>TNT MERCURIO CARGAS E ENCOMENDAS EXPRESSAS LT</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>312 FRETES E CARRETOS (2x)</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>03689570000129</t>
+        </is>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>TNT SUPRIMENTOS INDUSTRIAIS LTDA</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (4x), 321 MANUTENÇÃO E REPARO (2x)</t>
+        </is>
+      </c>
+      <c r="E119" s="10" t="inlineStr">
+        <is>
+          <t>misto - conferir o produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="12" t="inlineStr">
+        <is>
+          <t>01722256000175</t>
+        </is>
+      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
+          <t>UNIVAR SOLUTIONS BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (2x)</t>
+        </is>
+      </c>
+      <c r="E120" s="12" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="inlineStr">
+        <is>
+          <t>02033695000133</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>VEDAPACK EMBALAGENS INDUSTRIAIS LTDA.</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>56 MATÉRIA-PRIMA (1x)</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="12" t="inlineStr">
+        <is>
+          <t>06932964000154</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="inlineStr">
+        <is>
+          <t>VIP COMERCIO DE PLASTICOS LTDA</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>513 MATERIAL DE USO E CONSUMO (1x)</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>14587096000140</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>VON GRAFFEN E CREVELLONI LTDA</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>362 SERVIÇOS PRESTADOS POR TERCEIROS (1x)</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="12" t="inlineStr">
+        <is>
+          <t>02535864000729</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>VR BENEFICIOS E SERVICOS DE PROCESSAMENTO S.A</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>364 DESPESAS ADMINISTRATIVAS (4x)</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>52680145000184</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>YAHWEH PRINT BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>600 INSUMOS (8x)</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A4:E125"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Históricos padrão</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Histórico que o Domínio grava em cada tipo de lançamento das entradas (Lançamentos gerados pela Escrita). O nome do fornecedor aparece duas vezes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Histórico</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Formato</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>compra</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>COMPRAS DE MERCADORIAS NESTA DATA</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>&lt;HISTÓRICO&gt; &lt;nº doc&gt; &lt;NOME&gt; &lt;NOME&gt; &lt;CNPJ formatado&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>uso</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>COMPRAS PARA USO E CONSUMO</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>&lt;HISTÓRICO&gt; &lt;nº doc&gt; &lt;NOME&gt; &lt;NOME&gt; &lt;CNPJ formatado&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>devolucao</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>DEVOLUÇÃO VENDA NESTA DATA</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>&lt;HISTÓRICO&gt; &lt;nº doc&gt; &lt;NOME&gt; &lt;NOME&gt; &lt;CNPJ formatado&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>industrializacao</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>ENTRADA DE MERC. PARA INDUSTRIALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>&lt;HISTÓRICO&gt; &lt;nº doc&gt; &lt;NOME&gt; &lt;NOME&gt; &lt;CNPJ formatado&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>amostra</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>AMOSTRA GRATIS</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>&lt;HISTÓRICO&gt; &lt;nº doc&gt; &lt;NOME&gt; &lt;NOME&gt; &lt;CNPJ formatado&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>bonificacao</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>BONIFICAÇÕES RECEBIDAS</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>&lt;HISTÓRICO&gt; &lt;nº doc&gt; &lt;NOME&gt; &lt;NOME&gt; &lt;CNPJ formatado&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>remessa</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>REMESSA</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>&lt;HISTÓRICO&gt; &lt;nº doc&gt; &lt;NOME&gt; &lt;NOME&gt; &lt;CNPJ formatado&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>terceiros</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>INDUSTRIALIZAÇÃO EFETUADA POR TERCEIROS</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>&lt;HISTÓRICO&gt; &lt;nº doc&gt; &lt;NOME&gt; &lt;NOME&gt; &lt;CNPJ formatado&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>frete</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>SERVIÇO DE TRANSPORTE ADQUIRIDO</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>&lt;HISTÓRICO&gt; &lt;nº doc&gt; &lt;NOME&gt; &lt;NOME&gt; &lt;CNPJ formatado&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>servico</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>SERVIÇO TOMADO NESTA DATA</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>&lt;HISTÓRICO&gt; &lt;nº doc&gt; &lt;NOME&gt; &lt;NOME&gt; &lt;CNPJ formatado&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>recolher</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>VALOR A RECOLHER</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>sem documento (linha de retenção)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:C15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>